--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0090.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0090.xlsx
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Không xác định</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Feathered Tempest</t>
+          <t>Bão Tố Lông Vũ</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Yun Hezhui</t>
+          <t>Vân Hạt Chùy</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>The Knight's Faded Hours</t>
+          <t>Những Giờ Phút Phai Mờ Của Hiệp Sĩ</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Vững vàng trong điệu nhảy cuối cùng</t>
+          <t>Kiên Định Trong Vũ Điệu Cuối Cùng</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Do dự giữa gió và thủy triều</t>
+          <t>Do Dự Giữa Gió Cuốn Sóng Dâng</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Yet Within Solitude</t>
+          <t>Nhưng Trong Cô Đơn</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Hiệp sĩ lang thang tiến tới tự do</t>
+          <t>Hiệp Sĩ Lang Thang Hành Quân Tự Do</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Không xác định</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Howling Flame</t>
+          <t>Lửa Gào Thét</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Shuo Xiaotu</t>
+          <t>Thuyết Tiểu Đồ</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Worn Wooden Kiếm</t>
+          <t>Thanh Kiếm Gỗ Mòn Vẹt</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Golden Laurel</t>
+          <t>Vòng Nguyệt Quế Vàng</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Hand Puppets</t>
+          <t>Múa rối tay</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Old Medal</t>
+          <t>Huy Chương Cũ</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Viburnum Bouquet</t>
+          <t>Bó Hoa Viburnum</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Mini Ta-da Figurines</t>
+          <t>Mô hình Mini Ta-da</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Burning Inside</t>
+          <t>Lửa Cháy Bên Trong</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Trên ngọn đồi</t>
+          <t>Lên Đỉnh Đồi</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>The Lone Wolf</t>
+          <t>Sói Cô Độc</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>The Nameless</t>
+          <t>Kẻ Vô Danh</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Big Little Things</t>
+          <t>Những Điều Nhỏ Nhặt Nhưng Lớn Lao</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Discard</t>
+          <t>Hủy Bỏ</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Save</t>
+          <t>Lưu</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Hoàn thành tất cả mục tiêu thử thách thời hạn</t>
+          <t>Hoàn thành tất cả mục tiêu thử thách giới hạn thời gian.</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Tiêu Chuẩn Deck I</t>
+          <t>Bộ Thẻ I Tiêu Chuẩn</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Tiêu Chuẩn Deck II</t>
+          <t>Bộ Thẻ II Tiêu Chuẩn</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Primary Build I</t>
+          <t>Cấu Hình Cơ Bản I</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Primary Build II</t>
+          <t>Cấu Hình Cơ Bản II</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Fortress I</t>
+          <t>Pháo Đài I</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Fortress II</t>
+          <t>Pháo Đài II</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Fortress III</t>
+          <t>Pháo Đài III</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Không Retreat I</t>
+          <t>Không Rút Lui I</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Không Retreat II</t>
+          <t>Không Rút Lui II</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Không Retreat III</t>
+          <t>Không Rút Lui III</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Luật Rừng I</t>
+          <t>Luật Rừng Xanh I</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Luật Rừng II</t>
+          <t>Luật Rừng Xanh II</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Luật Rừng III</t>
+          <t>Luật Rừng Xanh III</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Flash Strike I</t>
+          <t>Đòn Chớp I</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Flash Strike II</t>
+          <t>Đòn Chớp II</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Flash Strike III</t>
+          <t>Đòn Chớp III</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Biến Đổier I</t>
+          <t>Biến Hình Giả I</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Biến Đổier II</t>
+          <t>Biến Hình Giả II</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Biến Đổier III</t>
+          <t>Biến Hình Giả III</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Sức Mạnh Điều Chỉnh III</t>
+          <t>Điều Tần Cấp III</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Preset: Tiêu Chuẩn Deck</t>
+          <t>Bản dựng sẵn: Bộ bài Tiêu chuẩn</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Preset: Fortress</t>
+          <t>Cài Đặt: Pháo Đài Bất Diệt</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Preset: Không Retreat</t>
+          <t>Cài Đặt: Không Lùi Bước</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Bản dựng sẵn: Luật Rừng Xanh</t>
+          <t>Cài Đặt: Luật Rừng Hoang</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Preset: Flash Strike</t>
+          <t>Cài Đặt: Đòn Tấn Công Chớp Nhoáng</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Preset: Biến Đổier</t>
+          <t>Bản dựng sẵn: Biến Đổi</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Bản dựng sẵn: Sức Mạnh Điều Chỉnh</t>
+          <t>Bản dựng sẵn: Power of Modulation</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18004,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Không thể loại bỏ Echo có Cost 4</t>
+          <t>Chi phí 4 Echo không thể loại bỏ</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Anniversary</t>
+          <t>Kỷ niệm</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Tối đa 20 ký tự</t>
+          <t>Tối đa 20 nhân vật</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18284,7 +18284,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Bitter Fruits</t>
+          <t>Trái đắng</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Bouquet</t>
+          <t>Bó Hoa</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Afterglow</t>
+          <t>Hậu Quang</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Doomsday</t>
+          <t>Ngày Tận Thế</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Từ Vực Sâu Đại Dương</t>
+          <t>Từ Vực Thẳm Đại Dương</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Bóng Tối Vinh Quang</t>
+          <t>Bóng Tối Của Vinh Quang</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>The Search</t>
+          <t>Cuộc Tìm Kiếm</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>A Wolf's Companion</t>
+          <t>Người Bạn Đồng Hành Của Sói</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Finale's Respite</t>
+          <t>Khoảnh Khắc Nghỉ Ngơi Cuối Cùng</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>The Last Fight</t>
+          <t>Trận Chiến Cuối Cùng</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Reunion</t>
+          <t>Đoàn tụ</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Gem</t>
+          <t>Ngọc quý</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Echo Aspects</t>
+          <t>Các Thuộc Tính Echo</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Nhận trang phục mới</t>
+          <t>Nhận được trang phục mới</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Nhận Aspect mới</t>
+          <t>Nhận được Tướng mới</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Narration</t>
+          <t>Lời Tự Sự</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Hoàn thành Chương II Hồi III Nhiệm Vụ Chính để mở khóa</t>
+          <t>Hoàn thành Chương II Hồi III của Nhiệm Vụ Chính để mở khóa</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Chính Chương II Hồi III "Điều Hôm Qua Khóc, Hôm Nay Hát"</t>
+          <t>Hoàn thành Chương II Hồi III "Điều Hôm Qua Khóc, Hôm Nay Hát" của Nhiệm Vụ Chính</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Duelist Nâng cấp</t>
+          <t>Nâng Cấp Đấu Sĩ</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Collections</t>
+          <t>Bộ Sưu Tập</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Challenges</t>
+          <t>Thử Thách</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20524,7 +20524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Phần thưởng Thử thách</t>
+          <t>Phần Thưởng Thử Thách</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Phần Thưởng Đấu Trường</t>
+          <t>Phần Thưởng Đối Kháng</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>The Death Defier</t>
+          <t>Kẻ Thách Thức Tử Thần</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>[Septimont Travel Guide I]</t>
+          <t>["Cẩm Nang Du Lịch Septimont I"]</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>[Septimont Travel Guide II]</t>
+          <t>["Cẩm Nang Du Lịch Septimont II"]</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>"Script"</t>
+          <t>"Kịch bản"</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21084,7 +21084,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>"Script"</t>
+          <t>"Kịch bản"</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21154,7 +21154,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>Nguồn Cội</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Fiction</t>
+          <t>Ảo Tưởng</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Reality</t>
+          <t>Thực tại</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Thẻ mới</t>
+          <t>Thẻ Mới (Đã Mở Khóa)</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>New Card Frame</t>
+          <t>Khung Thẻ Mới</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Tôi Bắt Được Một Mephis! Không, Đợi Đã—Đó Là Kelpie</t>
+          <t>Ta bắt được một con Mephis! Không, khoan... nó là Kelpie.</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Thu Hoạch Đầy Đủ Từ Vực Sâu</t>
+          <t>Kéo Lưới Từ Vực Sâu</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Incandescent Eyrie</t>
+          <t>Thành Điểu Huyền Diệm</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21854,7 +21854,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Cloud Illumination</t>
+          <t>Ánh Sáng Mây Trời</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Những Cột Lửa</t>
+          <t>Trụ Lửa</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Đã Dùng Hết</t>
+          <t>Đã dùng hết rồi</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Nhiệm Vụ Sự Kiện</t>
+          <t>Nhiệm vụ sự kiện</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -22134,7 +22134,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Radiant Selection</t>
+          <t>Lựa Chọn Rạng Ngời</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Chiến thuật</t>
+          <t>Chiến Thuật</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22344,7 +22344,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Index</t>
+          <t>Mục lục</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Phần Thưởng Giới Hạn Thời Gian</t>
+          <t>Phần Thưởng Giới Hạn</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Proceed</t>
+          <t>Tiến lên</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Hoàn Thành Nhiệm Vụ Chính "Ngọn Lửa Trong Tim" Để Có Trải Nghiệm Tốt Hơn</t>
+          <t>Hoàn thành Nhiệm Vụ Chính "Flames of Heart" để có trải nghiệm tốt hơn</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Giấc Mơ Của Sự Chuyển Tiếp</t>
+          <t>Giấc Mộng Phân Tầng</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Giấc Mơ Nuốt Chửng</t>
+          <t>Giấc Mộng Nuốt Chửng</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Giấc Mơ Trao Đổi</t>
+          <t>Giấc Mộng Trao Đổi</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Giấc Mơ Hòa Nhập</t>
+          <t>Giấc Mộng Hòa Nhập</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22904,7 +22904,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Giấc Mơ Kết Nối</t>
+          <t>Giấc Mộng Kết Nối</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Test Run</t>
+          <t>Chạy thử</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Celestial Stairway</t>
+          <t>Thang Thiên Cổ</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Whirling Rapids</t>
+          <t>Dòng Nước Xoáy Cuồn Cuộn</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Dream: Infinite I</t>
+          <t>Giấc Mơ: Vô Tận I</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Barter Street</t>
+          <t>Phố Đổi Hàng</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Scriptless Show</t>
+          <t>Biểu Diễn Không Kịch Bản</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Dream: Infinite II</t>
+          <t>Giấc Mơ: Vô Tận II</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Sacrifice Night</t>
+          <t>Đêm Hy Sinh</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Mirror Maze</t>
+          <t>Mê Cung Gương</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23604,7 +23604,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Dream: Infinite III</t>
+          <t>Giấc Mơ: Vô Tận III</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Abyssal Mercator</t>
+          <t>Thương Nhân Vực Sâu</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Questless Knight</t>
+          <t>Hiệp Sĩ Không Nhiệm Vụ</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Abyssal Gladius</t>
+          <t>Kiếm Vực Sâu</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -24024,7 +24024,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Nimbus Wraith</t>
+          <t>Hồn Ma Nimbus</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Chest Mimic</t>
+          <t>Rương Biến Hình</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Hocus Pocus</t>
+          <t>Ảo thuật biến!</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Diggy Duggy</t>
+          <t>Đào Đi Đào Đi</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Dragon of Dirge</t>
+          <t>Rồng Than Khóc</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -25214,7 +25214,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Chop Chop</t>
+          <t>Nhanh lên nào</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Chop Chop: Headless</t>
+          <t>Chop Chop: Không Đầu</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Chop Chop: Leftless</t>
+          <t>Chop Chop: Không Tay Trái</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25564,7 +25564,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Baby Roseshroom</t>
+          <t>Nấm Hồng Bé Nhỏ</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25634,7 +25634,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Chop Chop: Rightless</t>
+          <t>Chop Chop: Không Tay Phải</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25774,7 +25774,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Vitreum Dancer</t>
+          <t>Vũ Công Pha Lê</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Autopuppet Scout</t>
+          <t>Trinh Sát Tự Động</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -25914,7 +25914,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Carapace</t>
+          <t>Vỏ giáp</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Golden Junrock</t>
+          <t>Junrock Vàng</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26264,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Nổi Giận Với Bức Tượng</t>
+          <t>Nổi Giận Trước Bức Tượng</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Abyssal Patricius</t>
+          <t>Quý Tộc Vực Sâu</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Calcified Junrock</t>
+          <t>Đá Junrock Hóa Thạch</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Mở Khóa Sau Khi Đến Đỉnh Capitoline Trong Nhiệm Vụ Chính "Bóng Tối Vinh Quang"</t>
+          <t>Mở khóa sau khi đặt chân đến Đồi Capitoline trong Nhiệm Vụ Chính "Bóng Tối Vinh Quang."</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Cờ Danh Vọng</t>
+          <t>Lá Cờ Danh Vọng</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27104,7 +27104,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Game Tokens</t>
+          <t>Mã Trò Chơi</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Commemorative Tickets</t>
+          <t>Vé Kỷ Niệm</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27244,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Pinwheel</t>
+          <t>Chong Chóng Gió</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Fantasia Hat</t>
+          <t>Mũ Fantasia</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27384,7 +27384,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Surprise Box</t>
+          <t>Hộp Bất Ngờ</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Chill Moment</t>
+          <t>Khoảnh khắc lạnh lẽo</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27524,7 +27524,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Paper Cranes</t>
+          <t>Hạc Giấy</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Rubber Junrock</t>
+          <t>Đá Junrock Cao Su</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Unity Band</t>
+          <t>Dải Băng Đoàn Kết</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27734,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Clockwork Illuminator</t>
+          <t>Người Chiếu Sáng Cơ Khí</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Moment</t>
+          <t>Khoảnh khắc</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Stamp Book</t>
+          <t>Sổ Tem</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -28014,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Figurine: Clang Bang</t>
+          <t>Mô hình: Clang Bang</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Dream Bubble</t>
+          <t>Bong Bóng Mộng</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Unstoppable Impact</t>
+          <t>Cú Đánh Không Thể Ngăn Cản</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Time Mailbox</t>
+          <t>Hòm Thư Thời Gian</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28294,7 +28294,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Giấc Mơ Quanh Quẩn</t>
+          <t>Vòng Xoáy Giấc Mơ</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Seesaw</t>
+          <t>Bập bênh</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Rotating Music Box</t>
+          <t>Hộp Nhạc Xoay</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Somnoire Eye</t>
+          <t>Con Mắt Somnoire</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28574,7 +28574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Dreamcatcher</t>
+          <t>Kẻ Bắt Giấc Mơ</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Dream Maze</t>
+          <t>Mê Cung Giấc Mơ</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28714,7 +28714,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Dreamland Cassette</t>
+          <t>Băng Cassette Giấc Mơ</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Accelerating Hourglass</t>
+          <t>Đồng Hồ Cát Tăng Tốc</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28854,7 +28854,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Blessing Garland</t>
+          <t>Vòng Hoa Phước Lành</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Fortune Bell</t>
+          <t>Chuông May Mắn</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Magic Pocket Watch</t>
+          <t>Đồng Hồ Bỏ Túi Ảo Thuật</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29134,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Color Coating</t>
+          <t>Phối Màu</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29274,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Figurine: Conductor</t>
+          <t>Mô hình: Nhạc Trưởng</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Dreamscape Train</t>
+          <t>Đoàn Tàu Mộng Ảo</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Chop Chop Balloon</t>
+          <t>Bong Bóng Nhanh Lên</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29484,7 +29484,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Fantasy Tree</t>
+          <t>Cây Ảo Ảnh</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Dreamy Firework</t>
+          <t>Pháo Hoa Mộng Mơ</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29624,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Lost Puzzle Piece</t>
+          <t>Mảnh Ghép Bí Ẩn Lạc Mất</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Brick World</t>
+          <t>Thế Giới Gạch</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29764,7 +29764,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Fusion Cube</t>
+          <t>Khối Hợp Thể</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29834,7 +29834,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Kaleidoscope</t>
+          <t>Kính Vạn Hoa</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Blessing: Add-on</t>
+          <t>Phúc Lành: Phụ Trợ</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Blessing: Transience</t>
+          <t>Phúc Lành: Phù Du</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30044,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Blessing: Đặt lại</t>
+          <t>Phúc Lành: Thiết Lập Lại</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30114,7 +30114,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Blessing: Teleport</t>
+          <t>Phúc Lành: Dịch Chuyển</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30184,7 +30184,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Hoàn Thành Echo Recruitment Để Bắt Đầu Ngày Tiếp Theo</t>
+          <t>Hoàn thành Tuyển dụng Echo để bắt đầu ngày tiếp theo</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Novice Duelist</t>
+          <t>Duel Tân Thủ</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Apprentice Duelist</t>
+          <t>Duelist Tập Sự</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Trained Duelist</t>
+          <t>Duelist Đã Tôi Luyện</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30464,7 +30464,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Skilled Duelist</t>
+          <t>Đấu sĩ tài ba</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30534,7 +30534,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Expert Duelist</t>
+          <t>Bậc Thầy Đấu Kiếm</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Master Duelist</t>
+          <t>Bậc Thầy Đấu Thủ</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30674,7 +30674,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Legendary Duelist</t>
+          <t>Đấu Sĩ Huyền Thoại</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Apex Duelist</t>
+          <t>Duelist Đỉnh Cao</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30814,7 +30814,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Echo Collection Unlocked</t>
+          <t>Đã Mở Khóa Thu Thập Tiếng Vọng</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Resonator Tactics Unlocked</t>
+          <t>Đã Mở Khóa Chiến Thuật Resonator</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -30954,7 +30954,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Không New Feature Available</t>
+          <t>Không Có Tính Năng Mới</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31024,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Mở Khóa Xây Dựng Bộ Free Deck Và Thiết Lập Echo</t>
+          <t>Mở khóa xây dựng Bộ bài và thiết lập Echo miễn phí</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31094,7 +31094,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Novice Medal Unlocked</t>
+          <t>Mở Khóa Huy Chương Tân Thủ</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31164,7 +31164,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Mở Khóa Tăng Tốc Giai Đoạn Chiến Đấu</t>
+          <t>Tăng Tốc Giai Đoạn Chiến Đấu Đã Mở Khóa</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31234,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Không New Feature Available</t>
+          <t>Không Có Tính Năng Mới</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31304,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Mở Khóa Nâng Cấp Endless Challenge - Thường Và Echo Appearance</t>
+          <t>Thử Thách Vô Tận - Bình Thường và Nâng Cấp Ngoại Hình Echo đã mở khóa</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31374,7 +31374,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Không New Feature Available</t>
+          <t>Không Có Tính Năng Mới</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Mở Khóa Endless Challenge - Difficult Và Huy Chương Thực Tập Sinh</t>
+          <t>Thử Thách Vô Tận - Cấp Độ Khó và Huy Chương Tập Sự Đã Mở Khóa</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Tất cả Features Unlocked</t>
+          <t>Tất cả tính năng đã mở khóa</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31584,7 +31584,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Tất cả Features Unlocked</t>
+          <t>Tất cả tính năng đã mở khóa</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31654,7 +31654,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Tất cả Features Unlocked</t>
+          <t>Tất cả tính năng đã mở khóa</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Tất cả Features Unlocked</t>
+          <t>Tất cả tính năng đã mở khóa</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Adept Medal Unlocked</t>
+          <t>Mở Khóa Huy Chương Tinh Anh</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31864,7 +31864,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Tất cả Features Unlocked</t>
+          <t>Tất cả tính năng đã mở khóa</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Tất cả Features Unlocked</t>
+          <t>Tất cả tính năng đã mở khóa</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Tất cả Features Unlocked</t>
+          <t>Tất cả tính năng đã mở khóa</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Tất cả Features Unlocked</t>
+          <t>Tất cả tính năng đã mở khóa</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Veteran Medal Unlocked</t>
+          <t>Huy Chương Kì Cựu Đã Mở Khóa</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32214,7 +32214,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Chức năng bị khóa, hãy tăng cấp để tiếp tục</t>
+          <t>Chức năng bị khóa, hãy tăng cấp để mở khóa</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Chức năng bị khóa, hãy tăng cấp để mở</t>
+          <t>Chức năng bị khóa, hãy tăng cấp để mở khóa</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32354,7 +32354,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Chức năng bị khóa, hãy tăng cấp để mở</t>
+          <t>Chức năng bị khóa, hãy tăng cấp để mở khóa</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32494,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Rời khỏi</t>
+          <t>Rời đi</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Wooly-Counting Game</t>
+          <t>Trò Đếm Cừu Wooly</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Frosty Gusto</t>
+          <t>Hơi Thở Băng Giá</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32774,7 +32774,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Phantom Hunter</t>
+          <t>Thợ Săn Ảo Ảnh</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32844,7 +32844,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Cleansing Reflections</t>
+          <t>Những Phản Chiếu Thanh Tẩy</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32914,7 +32914,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Nature Calling</t>
+          <t>Tiếng Gọi Của Tự Nhiên</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -32984,7 +32984,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Thử Thách Vô Tận - Thường</t>
+          <t>Thử Thách Vô Tận - Bình Thường</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33054,7 +33054,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Thử Thách Vô Tận - Khó</t>
+          <t>Thử Thách Vô Tận - Cấp Độ Khó</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33194,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>The Duelist's Path</t>
+          <t>Con đường của Kẻ Duel</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33264,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Curio's Keepsake</t>
+          <t>Di Vật Của Curio</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33334,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Ironheart Medal</t>
+          <t>Huy Chương Thép Tim</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33404,7 +33404,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Splendent Medal</t>
+          <t>Huy Chương Rực Rỡ</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33474,7 +33474,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Lifespring Medal</t>
+          <t>Huy Chương Lifespring</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33544,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Dustbound Medal</t>
+          <t>Huy Chương Bám Bụi</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Nightmare Medal</t>
+          <t>Huy Chương Ác Mộng</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33684,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Firebrand Medal</t>
+          <t>Huy Chương Lửa Thiêng</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33754,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Novice Medal</t>
+          <t>Huy Chương Tân Thủ</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Trainee Medal</t>
+          <t>Huy Chương Tập Sự</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Adept Medal</t>
+          <t>Huy Chương Tinh Anh</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33964,7 +33964,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Veteran Medal</t>
+          <t>Huy Chương Kì Cựu</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34034,7 +34034,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Victor Medal</t>
+          <t>Huy chương Victor</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Conqueror Medal</t>
+          <t>Huy chương Chinh Phục</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34174,7 +34174,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Shanty Medal</t>
+          <t>Huy chương Shanty</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34244,7 +34244,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Passion Medal</t>
+          <t>Huy Chương Đam Mê</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34314,7 +34314,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Ballad Medal</t>
+          <t>Huy chương Ballad</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34384,7 +34384,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Hound Medal</t>
+          <t>Huy Chương Hound</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34454,7 +34454,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Ancient Legacy Medal</t>
+          <t>Huy Chương Di Sản Cổ Đại</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Supreme Echo Medal</t>
+          <t>Huy Chương Echo Tối Thượng</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34594,7 +34594,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Hoàn thành 3 Chương bất kỳ của Nhiệm Vụ Chính</t>
+          <t>Hoàn thành 3 Chương bất kỳ trong Nhiệm Vụ Chính.</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34664,7 +34664,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Hoàn thành 4 Chương bất kỳ của Nhiệm Vụ Chính</t>
+          <t>Hoàn thành 4 Chương bất kỳ trong Nhiệm Vụ Chính.</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34734,7 +34734,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Hoàn thành 5 Chương bất kỳ của Nhiệm Vụ Chính</t>
+          <t>Hoàn thành 5 Chương bất kỳ trong Nhiệm Vụ Chính.</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34804,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Hoàn thành 1 Câu Chuyện Đồng Hành bất kỳ</t>
+          <t>Hoàn thành 1 Câu Chuyện Đồng Hành bất kỳ.</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Thu thập 6 Huy Hiệu tại Tower Vọng Tiếng trong Khu Vực Thử Nghiệm Tower of Adversity</t>
+          <t>Thu thập 6 Huy Hiệu tại Tháp Vọng Tiếng trong Khu Vực Thử Nghiệm Tháp Nghịch Cảnh</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34944,7 +34944,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>New Resonator Tactics</t>
+          <t>Chiến Thuật Cộng Hưởng Mới</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Huy Chương Uy Tín Mới</t>
+          <t>Huy Chương Uy Danh Mới</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35084,7 +35084,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Rover's Tactics Unlocked</t>
+          <t>Đã Mở Khóa Chiến Thuật cho Vận Mệnh Giả</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35154,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Encore's Tactics Unlocked</t>
+          <t>Encore Mở Khóa Chiến Thuật</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35224,7 +35224,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Zani's Tactics Unlocked</t>
+          <t>Chiến thuật của Zani đã mở khóa</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35294,7 +35294,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Cantarella's Tactics Unlocked</t>
+          <t>Chiến thuật của Cantarella đã mở khóa</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35364,7 +35364,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Xiangli Yao's Tactics Unlocked</t>
+          <t>Chiến thuật của Tương Lị Dao đã mở khóa</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -35434,7 +35434,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Carlotta's Tactics Unlocked</t>
+          <t>Mở khóa Chiến Thuật của Carlotta</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
